--- a/artfynd/A 38869-2025 artfynd.xlsx
+++ b/artfynd/A 38869-2025 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>127414747</v>
       </c>
       <c r="B4" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38869-2025 artfynd.xlsx
+++ b/artfynd/A 38869-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127414749</v>
       </c>
       <c r="B2" t="n">
-        <v>92648</v>
+        <v>92650</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127414748</v>
       </c>
       <c r="B3" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>127414747</v>
       </c>
       <c r="B4" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38869-2025 artfynd.xlsx
+++ b/artfynd/A 38869-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127414749</v>
       </c>
       <c r="B2" t="n">
-        <v>92650</v>
+        <v>92656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127414748</v>
       </c>
       <c r="B3" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>127414747</v>
       </c>
       <c r="B4" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38869-2025 artfynd.xlsx
+++ b/artfynd/A 38869-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127414749</v>
       </c>
       <c r="B2" t="n">
-        <v>92656</v>
+        <v>92659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127414748</v>
       </c>
       <c r="B3" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>127414747</v>
       </c>
       <c r="B4" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38869-2025 artfynd.xlsx
+++ b/artfynd/A 38869-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127414749</v>
       </c>
       <c r="B2" t="n">
-        <v>92659</v>
+        <v>92667</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127414748</v>
       </c>
       <c r="B3" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>127414747</v>
       </c>
       <c r="B4" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38869-2025 artfynd.xlsx
+++ b/artfynd/A 38869-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127414749</v>
       </c>
       <c r="B2" t="n">
-        <v>92667</v>
+        <v>92668</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127414748</v>
       </c>
       <c r="B3" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>127414747</v>
       </c>
       <c r="B4" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38869-2025 artfynd.xlsx
+++ b/artfynd/A 38869-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127414749</v>
       </c>
       <c r="B2" t="n">
-        <v>92668</v>
+        <v>92669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127414748</v>
       </c>
       <c r="B3" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>127414747</v>
       </c>
       <c r="B4" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38869-2025 artfynd.xlsx
+++ b/artfynd/A 38869-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127414749</v>
       </c>
       <c r="B2" t="n">
-        <v>92669</v>
+        <v>92670</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127414748</v>
       </c>
       <c r="B3" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>127414747</v>
       </c>
       <c r="B4" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
